--- a/produtos/Relatorio_QAQC_Dados_Censurados.xlsx
+++ b/produtos/Relatorio_QAQC_Dados_Censurados.xlsx
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -617,7 +617,7 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -634,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -719,7 +719,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -770,13 +770,13 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>10.8</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -787,13 +787,13 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -804,10 +804,10 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -821,13 +821,13 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E15">
-        <v>91.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -838,13 +838,13 @@
         <v>12</v>
       </c>
       <c r="C16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E16">
-        <v>95.2</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -855,10 +855,10 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -872,13 +872,13 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E18">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -889,13 +889,13 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -906,13 +906,13 @@
         <v>13</v>
       </c>
       <c r="C20">
+        <v>23</v>
+      </c>
+      <c r="D20">
         <v>21</v>
       </c>
-      <c r="D20">
-        <v>19</v>
-      </c>
       <c r="E20">
-        <v>90.5</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -923,13 +923,13 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21">
-        <v>66.7</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -940,13 +940,13 @@
         <v>14</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>47.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -957,13 +957,13 @@
         <v>14</v>
       </c>
       <c r="C23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>61.9</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -974,13 +974,13 @@
         <v>14</v>
       </c>
       <c r="C24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24">
-        <v>73.7</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -991,13 +991,13 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>56.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1008,13 +1008,13 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>34.8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1025,13 +1025,13 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>30.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1042,13 +1042,13 @@
         <v>15</v>
       </c>
       <c r="C28">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1059,13 +1059,13 @@
         <v>15</v>
       </c>
       <c r="C29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>26.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1076,13 +1076,13 @@
         <v>16</v>
       </c>
       <c r="C30">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>65.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1093,13 +1093,13 @@
         <v>16</v>
       </c>
       <c r="C31">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D31">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E31">
-        <v>69.59999999999999</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1110,13 +1110,13 @@
         <v>16</v>
       </c>
       <c r="C32">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>71.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1127,13 +1127,13 @@
         <v>16</v>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33">
-        <v>55.6</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="C34">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E34">
-        <v>56.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1161,13 +1161,13 @@
         <v>17</v>
       </c>
       <c r="C35">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E35">
-        <v>56.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1178,13 +1178,13 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>52.4</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1195,13 +1195,13 @@
         <v>17</v>
       </c>
       <c r="C37">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>72.2</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1212,13 +1212,13 @@
         <v>18</v>
       </c>
       <c r="C38">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>52.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1229,13 +1229,13 @@
         <v>18</v>
       </c>
       <c r="C39">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E39">
-        <v>47.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1246,13 +1246,13 @@
         <v>18</v>
       </c>
       <c r="C40">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1263,13 +1263,13 @@
         <v>18</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D41">
         <v>10</v>
       </c>
       <c r="E41">
-        <v>55.6</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1280,13 +1280,13 @@
         <v>19</v>
       </c>
       <c r="C42">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D42">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E42">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1297,13 +1297,13 @@
         <v>19</v>
       </c>
       <c r="C43">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D43">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E43">
-        <v>91.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1314,13 +1314,13 @@
         <v>20</v>
       </c>
       <c r="C44">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D44">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>78.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1331,13 +1331,13 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E45">
-        <v>82.59999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1348,13 +1348,13 @@
         <v>20</v>
       </c>
       <c r="C46">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D46">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>81</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1365,13 +1365,13 @@
         <v>20</v>
       </c>
       <c r="C47">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>72.2</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1433,7 +1433,7 @@
         <v>22</v>
       </c>
       <c r="C51">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>22</v>
       </c>
       <c r="C52">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1467,13 +1467,13 @@
         <v>22</v>
       </c>
       <c r="C53">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1484,7 +1484,7 @@
         <v>22</v>
       </c>
       <c r="C54">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>23</v>
       </c>
       <c r="C55">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>23</v>
       </c>
       <c r="C56">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>23</v>
       </c>
       <c r="C57">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -1552,7 +1552,7 @@
         <v>23</v>
       </c>
       <c r="C58">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1569,13 +1569,13 @@
         <v>24</v>
       </c>
       <c r="C59">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D59">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E59">
-        <v>82.59999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1586,13 +1586,13 @@
         <v>24</v>
       </c>
       <c r="C60">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D60">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E60">
-        <v>91.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1603,13 +1603,13 @@
         <v>24</v>
       </c>
       <c r="C61">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D61">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E61">
-        <v>85.7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1620,13 +1620,13 @@
         <v>24</v>
       </c>
       <c r="C62">
+        <v>19</v>
+      </c>
+      <c r="D62">
         <v>18</v>
       </c>
-      <c r="D62">
-        <v>17</v>
-      </c>
       <c r="E62">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1637,13 +1637,13 @@
         <v>25</v>
       </c>
       <c r="C63">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D63">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E63">
-        <v>91.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1654,13 +1654,13 @@
         <v>25</v>
       </c>
       <c r="C64">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D64">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E64">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1671,13 +1671,13 @@
         <v>25</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D65">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E65">
-        <v>95.2</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1688,13 +1688,13 @@
         <v>25</v>
       </c>
       <c r="C66">
+        <v>19</v>
+      </c>
+      <c r="D66">
         <v>18</v>
       </c>
-      <c r="D66">
-        <v>17</v>
-      </c>
       <c r="E66">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1705,13 +1705,13 @@
         <v>26</v>
       </c>
       <c r="C67">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D67">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E67">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1722,13 +1722,13 @@
         <v>26</v>
       </c>
       <c r="C68">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D68">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E68">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1739,10 +1739,10 @@
         <v>26</v>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D69">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E69">
         <v>100</v>
@@ -1756,10 +1756,10 @@
         <v>26</v>
       </c>
       <c r="C70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D70">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E70">
         <v>100</v>
@@ -1773,13 +1773,13 @@
         <v>27</v>
       </c>
       <c r="C71">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D71">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E71">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1790,13 +1790,13 @@
         <v>27</v>
       </c>
       <c r="C72">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D72">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E72">
-        <v>82.59999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1807,13 +1807,13 @@
         <v>27</v>
       </c>
       <c r="C73">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D73">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E73">
-        <v>71.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1824,13 +1824,13 @@
         <v>27</v>
       </c>
       <c r="C74">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E74">
-        <v>72.2</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1841,13 +1841,13 @@
         <v>28</v>
       </c>
       <c r="C75">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="C76">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E76">
-        <v>13.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>28</v>
       </c>
       <c r="C77">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D77">
         <v>2</v>
       </c>
       <c r="E77">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>28</v>
       </c>
       <c r="C78">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D78">
         <v>4</v>
       </c>
       <c r="E78">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1909,7 +1909,7 @@
         <v>29</v>
       </c>
       <c r="C79">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>29</v>
       </c>
       <c r="C80">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
       <c r="E80">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>29</v>
       </c>
       <c r="C81">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>29</v>
       </c>
       <c r="C82">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D82">
         <v>2</v>
       </c>
       <c r="E82">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1977,10 +1977,10 @@
         <v>30</v>
       </c>
       <c r="C83">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D83">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E83">
         <v>100</v>
@@ -1994,10 +1994,10 @@
         <v>30</v>
       </c>
       <c r="C84">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D84">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E84">
         <v>100</v>
@@ -2011,10 +2011,10 @@
         <v>30</v>
       </c>
       <c r="C85">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D85">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E85">
         <v>100</v>
@@ -2028,10 +2028,10 @@
         <v>30</v>
       </c>
       <c r="C86">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D86">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E86">
         <v>100</v>
@@ -2045,10 +2045,10 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D87">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E87">
         <v>100</v>
@@ -2062,13 +2062,13 @@
         <v>31</v>
       </c>
       <c r="C88">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D88">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E88">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2079,10 +2079,10 @@
         <v>31</v>
       </c>
       <c r="C89">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D89">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E89">
         <v>100</v>
@@ -2096,10 +2096,10 @@
         <v>31</v>
       </c>
       <c r="C90">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D90">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E90">
         <v>100</v>
@@ -2113,13 +2113,13 @@
         <v>32</v>
       </c>
       <c r="C91">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D91">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E91">
-        <v>91.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2130,10 +2130,10 @@
         <v>32</v>
       </c>
       <c r="C92">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D92">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E92">
         <v>100</v>
@@ -2147,10 +2147,10 @@
         <v>32</v>
       </c>
       <c r="C93">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D93">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E93">
         <v>100</v>
@@ -2164,13 +2164,13 @@
         <v>32</v>
       </c>
       <c r="C94">
+        <v>19</v>
+      </c>
+      <c r="D94">
         <v>18</v>
       </c>
-      <c r="D94">
-        <v>17</v>
-      </c>
       <c r="E94">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2181,10 +2181,10 @@
         <v>33</v>
       </c>
       <c r="C95">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D95">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E95">
         <v>100</v>
@@ -2198,10 +2198,10 @@
         <v>33</v>
       </c>
       <c r="C96">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D96">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E96">
         <v>100</v>
@@ -2215,10 +2215,10 @@
         <v>33</v>
       </c>
       <c r="C97">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D97">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E97">
         <v>100</v>
@@ -2232,10 +2232,10 @@
         <v>33</v>
       </c>
       <c r="C98">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D98">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E98">
         <v>100</v>
@@ -2249,13 +2249,13 @@
         <v>34</v>
       </c>
       <c r="C99">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D99">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E99">
-        <v>80</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2266,13 +2266,13 @@
         <v>34</v>
       </c>
       <c r="C100">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D100">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E100">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2283,13 +2283,13 @@
         <v>34</v>
       </c>
       <c r="C101">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D101">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E101">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2300,13 +2300,13 @@
         <v>34</v>
       </c>
       <c r="C102">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D102">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E102">
-        <v>89.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2317,13 +2317,13 @@
         <v>35</v>
       </c>
       <c r="C103">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D103">
         <v>2</v>
       </c>
       <c r="E103">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2334,13 +2334,13 @@
         <v>35</v>
       </c>
       <c r="C104">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2351,13 +2351,13 @@
         <v>35</v>
       </c>
       <c r="C105">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105">
-        <v>8.699999999999999</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2368,13 +2368,13 @@
         <v>35</v>
       </c>
       <c r="C106">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D106">
         <v>4</v>
       </c>
       <c r="E106">
-        <v>16</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2385,13 +2385,13 @@
         <v>36</v>
       </c>
       <c r="C107">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D107">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E107">
-        <v>56.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2402,13 +2402,13 @@
         <v>36</v>
       </c>
       <c r="C108">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D108">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E108">
-        <v>69.59999999999999</v>
+        <v>72</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2419,13 +2419,13 @@
         <v>36</v>
       </c>
       <c r="C109">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D109">
         <v>12</v>
       </c>
       <c r="E109">
-        <v>52.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2436,13 +2436,13 @@
         <v>36</v>
       </c>
       <c r="C110">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>26.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2453,7 +2453,7 @@
         <v>37</v>
       </c>
       <c r="C111">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>37</v>
       </c>
       <c r="C112">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2487,7 +2487,7 @@
         <v>37</v>
       </c>
       <c r="C113">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>37</v>
       </c>
       <c r="C114">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -2521,13 +2521,13 @@
         <v>38</v>
       </c>
       <c r="C115">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D115">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E115">
-        <v>62.5</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2538,13 +2538,13 @@
         <v>38</v>
       </c>
       <c r="C116">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D116">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E116">
-        <v>40</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2555,13 +2555,13 @@
         <v>38</v>
       </c>
       <c r="C117">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D117">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E117">
-        <v>62.5</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2572,13 +2572,13 @@
         <v>38</v>
       </c>
       <c r="C118">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118">
         <v>10</v>
       </c>
       <c r="E118">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2589,10 +2589,10 @@
         <v>39</v>
       </c>
       <c r="C119">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D119">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E119">
         <v>100</v>
@@ -2606,10 +2606,10 @@
         <v>39</v>
       </c>
       <c r="C120">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D120">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E120">
         <v>100</v>
@@ -2623,10 +2623,10 @@
         <v>39</v>
       </c>
       <c r="C121">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D121">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E121">
         <v>100</v>
@@ -2640,10 +2640,10 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D122">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E122">
         <v>100</v>
@@ -2657,13 +2657,13 @@
         <v>40</v>
       </c>
       <c r="C123">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2674,13 +2674,13 @@
         <v>40</v>
       </c>
       <c r="C124">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2691,7 +2691,7 @@
         <v>40</v>
       </c>
       <c r="C125">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2708,13 +2708,13 @@
         <v>40</v>
       </c>
       <c r="C126">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2725,7 +2725,7 @@
         <v>41</v>
       </c>
       <c r="C127">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>41</v>
       </c>
       <c r="C128">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>41</v>
       </c>
       <c r="C129">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -2776,13 +2776,13 @@
         <v>41</v>
       </c>
       <c r="C130">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2793,13 +2793,13 @@
         <v>42</v>
       </c>
       <c r="C131">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D131">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E131">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2810,13 +2810,13 @@
         <v>42</v>
       </c>
       <c r="C132">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D132">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E132">
-        <v>78.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2827,13 +2827,13 @@
         <v>42</v>
       </c>
       <c r="C133">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D133">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E133">
-        <v>85.7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2844,13 +2844,13 @@
         <v>42</v>
       </c>
       <c r="C134">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D134">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E134">
-        <v>88.90000000000001</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2861,13 +2861,13 @@
         <v>43</v>
       </c>
       <c r="C135">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D135">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E135">
-        <v>91.3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2878,10 +2878,10 @@
         <v>43</v>
       </c>
       <c r="C136">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D136">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E136">
         <v>100</v>
@@ -2895,13 +2895,13 @@
         <v>43</v>
       </c>
       <c r="C137">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D137">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E137">
-        <v>95.2</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2912,13 +2912,13 @@
         <v>43</v>
       </c>
       <c r="C138">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D138">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E138">
-        <v>88.90000000000001</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2929,13 +2929,13 @@
         <v>44</v>
       </c>
       <c r="C139">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D139">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E139">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2946,13 +2946,13 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D140">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E140">
-        <v>95.7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2963,10 +2963,10 @@
         <v>44</v>
       </c>
       <c r="C141">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D141">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E141">
         <v>100</v>
@@ -2980,10 +2980,10 @@
         <v>44</v>
       </c>
       <c r="C142">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D142">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E142">
         <v>100</v>
@@ -2997,7 +2997,7 @@
         <v>45</v>
       </c>
       <c r="C143">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -3014,13 +3014,13 @@
         <v>45</v>
       </c>
       <c r="C144">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E144">
-        <v>19.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3031,13 +3031,13 @@
         <v>45</v>
       </c>
       <c r="C145">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E145">
-        <v>19</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3048,13 +3048,13 @@
         <v>45</v>
       </c>
       <c r="C146">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E146">
-        <v>13.3</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3065,13 +3065,13 @@
         <v>46</v>
       </c>
       <c r="C147">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D147">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E147">
-        <v>73.90000000000001</v>
+        <v>76</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3082,13 +3082,13 @@
         <v>46</v>
       </c>
       <c r="C148">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D148">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E148">
-        <v>65.2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3099,13 +3099,13 @@
         <v>46</v>
       </c>
       <c r="C149">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D149">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E149">
-        <v>71.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3116,13 +3116,13 @@
         <v>46</v>
       </c>
       <c r="C150">
+        <v>19</v>
+      </c>
+      <c r="D150">
         <v>18</v>
       </c>
-      <c r="D150">
-        <v>17</v>
-      </c>
       <c r="E150">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3133,7 +3133,7 @@
         <v>47</v>
       </c>
       <c r="C151">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>47</v>
       </c>
       <c r="C152">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>47</v>
       </c>
       <c r="C153">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>47</v>
       </c>
       <c r="C154">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -3201,10 +3201,10 @@
         <v>48</v>
       </c>
       <c r="C155">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D155">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E155">
         <v>100</v>
@@ -3218,10 +3218,10 @@
         <v>48</v>
       </c>
       <c r="C156">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D156">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E156">
         <v>100</v>
@@ -3235,10 +3235,10 @@
         <v>48</v>
       </c>
       <c r="C157">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D157">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E157">
         <v>100</v>
@@ -3252,10 +3252,10 @@
         <v>48</v>
       </c>
       <c r="C158">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D158">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E158">
         <v>100</v>
@@ -3269,13 +3269,13 @@
         <v>49</v>
       </c>
       <c r="C159">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D159">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E159">
-        <v>95.7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3286,10 +3286,10 @@
         <v>49</v>
       </c>
       <c r="C160">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D160">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E160">
         <v>100</v>
@@ -3303,13 +3303,13 @@
         <v>49</v>
       </c>
       <c r="C161">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D161">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E161">
-        <v>66.7</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3320,10 +3320,10 @@
         <v>49</v>
       </c>
       <c r="C162">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D162">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E162">
         <v>100</v>
@@ -3337,10 +3337,10 @@
         <v>50</v>
       </c>
       <c r="C163">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D163">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E163">
         <v>100</v>
@@ -3354,10 +3354,10 @@
         <v>50</v>
       </c>
       <c r="C164">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D164">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E164">
         <v>100</v>
@@ -3371,10 +3371,10 @@
         <v>51</v>
       </c>
       <c r="C165">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D165">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E165">
         <v>100</v>
@@ -3388,10 +3388,10 @@
         <v>51</v>
       </c>
       <c r="C166">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D166">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E166">
         <v>100</v>
@@ -3405,10 +3405,10 @@
         <v>51</v>
       </c>
       <c r="C167">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D167">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E167">
         <v>100</v>
@@ -3422,10 +3422,10 @@
         <v>51</v>
       </c>
       <c r="C168">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D168">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E168">
         <v>100</v>
@@ -3439,13 +3439,13 @@
         <v>52</v>
       </c>
       <c r="C169">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D169">
         <v>3</v>
       </c>
       <c r="E169">
-        <v>10.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3456,13 +3456,13 @@
         <v>52</v>
       </c>
       <c r="C170">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E170">
-        <v>30.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3473,13 +3473,13 @@
         <v>52</v>
       </c>
       <c r="C171">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D171">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E171">
-        <v>61.9</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3490,13 +3490,13 @@
         <v>52</v>
       </c>
       <c r="C172">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D172">
         <v>7</v>
       </c>
       <c r="E172">
-        <v>31.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3507,7 +3507,7 @@
         <v>53</v>
       </c>
       <c r="C173">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>53</v>
       </c>
       <c r="C174">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>53</v>
       </c>
       <c r="C175">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>53</v>
       </c>
       <c r="C176">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>54</v>
       </c>
       <c r="C177">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D177">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E177">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3592,13 +3592,13 @@
         <v>54</v>
       </c>
       <c r="C178">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D178">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E178">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3609,13 +3609,13 @@
         <v>54</v>
       </c>
       <c r="C179">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E179">
-        <v>7.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3626,13 +3626,13 @@
         <v>54</v>
       </c>
       <c r="C180">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D180">
         <v>9</v>
       </c>
       <c r="E180">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3694,13 +3694,13 @@
         <v>56</v>
       </c>
       <c r="C184">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184">
-        <v>4.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3711,13 +3711,13 @@
         <v>56</v>
       </c>
       <c r="C185">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E185">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3728,13 +3728,13 @@
         <v>56</v>
       </c>
       <c r="C186">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D186">
         <v>2</v>
       </c>
       <c r="E186">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3745,13 +3745,13 @@
         <v>56</v>
       </c>
       <c r="C187">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D187">
         <v>1</v>
       </c>
       <c r="E187">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4000,10 +4000,10 @@
         <v>62</v>
       </c>
       <c r="C202">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D202">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E202">
         <v>100</v>
@@ -4017,10 +4017,10 @@
         <v>62</v>
       </c>
       <c r="C203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E203">
         <v>100</v>
@@ -4034,13 +4034,13 @@
         <v>63</v>
       </c>
       <c r="C204">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D204">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E204">
-        <v>71.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4051,13 +4051,13 @@
         <v>63</v>
       </c>
       <c r="C205">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D205">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E205">
-        <v>77.8</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="206" spans="1:5">

--- a/produtos/Relatorio_QAQC_Dados_Censurados.xlsx
+++ b/produtos/Relatorio_QAQC_Dados_Censurados.xlsx
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -617,7 +617,7 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -634,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -719,7 +719,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -770,13 +770,13 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -787,13 +787,13 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -804,10 +804,10 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -821,13 +821,13 @@
         <v>12</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -838,13 +838,13 @@
         <v>12</v>
       </c>
       <c r="C16">
+        <v>24</v>
+      </c>
+      <c r="D16">
         <v>23</v>
       </c>
-      <c r="D16">
-        <v>22</v>
-      </c>
       <c r="E16">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -855,10 +855,10 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -872,13 +872,13 @@
         <v>13</v>
       </c>
       <c r="C18">
+        <v>26</v>
+      </c>
+      <c r="D18">
         <v>25</v>
       </c>
-      <c r="D18">
-        <v>24</v>
-      </c>
       <c r="E18">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -889,13 +889,13 @@
         <v>13</v>
       </c>
       <c r="C19">
+        <v>26</v>
+      </c>
+      <c r="D19">
         <v>25</v>
       </c>
-      <c r="D19">
-        <v>24</v>
-      </c>
       <c r="E19">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -906,13 +906,13 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>91.3</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -923,13 +923,13 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>13</v>
       </c>
       <c r="E21">
-        <v>68.40000000000001</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -940,13 +940,13 @@
         <v>14</v>
       </c>
       <c r="C22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>52.2</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -957,13 +957,13 @@
         <v>14</v>
       </c>
       <c r="C23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23">
-        <v>65.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -974,13 +974,13 @@
         <v>14</v>
       </c>
       <c r="C24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>76.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -991,13 +991,13 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25">
-        <v>58.8</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1008,13 +1008,13 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>40</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1025,13 +1025,13 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>36</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1042,13 +1042,13 @@
         <v>15</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>47.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1059,13 +1059,13 @@
         <v>15</v>
       </c>
       <c r="C29">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1076,13 +1076,13 @@
         <v>16</v>
       </c>
       <c r="C30">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30">
-        <v>68</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1093,13 +1093,13 @@
         <v>16</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
-        <v>72</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1110,13 +1110,13 @@
         <v>16</v>
       </c>
       <c r="C32">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32">
         <v>17</v>
       </c>
       <c r="E32">
-        <v>73.90000000000001</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1127,13 +1127,13 @@
         <v>16</v>
       </c>
       <c r="C33">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>57.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="C34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>60</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1161,13 +1161,13 @@
         <v>17</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1178,13 +1178,13 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>56.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1195,13 +1195,13 @@
         <v>17</v>
       </c>
       <c r="C37">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37">
-        <v>73.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1212,13 +1212,13 @@
         <v>18</v>
       </c>
       <c r="C38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38">
-        <v>56</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1229,13 +1229,13 @@
         <v>18</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>52</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1246,13 +1246,13 @@
         <v>18</v>
       </c>
       <c r="C40">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D40">
         <v>11</v>
       </c>
       <c r="E40">
-        <v>47.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1263,13 +1263,13 @@
         <v>18</v>
       </c>
       <c r="C41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41">
         <v>10</v>
       </c>
       <c r="E41">
-        <v>52.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1280,13 +1280,13 @@
         <v>19</v>
       </c>
       <c r="C42">
+        <v>26</v>
+      </c>
+      <c r="D42">
         <v>25</v>
       </c>
-      <c r="D42">
-        <v>24</v>
-      </c>
       <c r="E42">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1297,13 +1297,13 @@
         <v>19</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1314,13 +1314,13 @@
         <v>20</v>
       </c>
       <c r="C44">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E44">
-        <v>80</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1331,13 +1331,13 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D45">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E45">
-        <v>84</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1348,13 +1348,13 @@
         <v>20</v>
       </c>
       <c r="C46">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D46">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E46">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1365,13 +1365,13 @@
         <v>20</v>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>73.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1433,7 +1433,7 @@
         <v>22</v>
       </c>
       <c r="C51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>22</v>
       </c>
       <c r="C52">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1467,13 +1467,13 @@
         <v>22</v>
       </c>
       <c r="C53">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1484,7 +1484,7 @@
         <v>22</v>
       </c>
       <c r="C54">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>23</v>
       </c>
       <c r="C55">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>23</v>
       </c>
       <c r="C56">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>23</v>
       </c>
       <c r="C57">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -1552,7 +1552,7 @@
         <v>23</v>
       </c>
       <c r="C58">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1569,13 +1569,13 @@
         <v>24</v>
       </c>
       <c r="C59">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D59">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E59">
-        <v>84</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1586,13 +1586,13 @@
         <v>24</v>
       </c>
       <c r="C60">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1603,13 +1603,13 @@
         <v>24</v>
       </c>
       <c r="C61">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D61">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E61">
-        <v>87</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1620,13 +1620,13 @@
         <v>24</v>
       </c>
       <c r="C62">
+        <v>20</v>
+      </c>
+      <c r="D62">
         <v>19</v>
       </c>
-      <c r="D62">
-        <v>18</v>
-      </c>
       <c r="E62">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1637,13 +1637,13 @@
         <v>25</v>
       </c>
       <c r="C63">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E63">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1654,13 +1654,13 @@
         <v>25</v>
       </c>
       <c r="C64">
+        <v>26</v>
+      </c>
+      <c r="D64">
         <v>25</v>
       </c>
-      <c r="D64">
-        <v>24</v>
-      </c>
       <c r="E64">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1671,13 +1671,13 @@
         <v>25</v>
       </c>
       <c r="C65">
+        <v>24</v>
+      </c>
+      <c r="D65">
         <v>23</v>
       </c>
-      <c r="D65">
-        <v>22</v>
-      </c>
       <c r="E65">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1688,13 +1688,13 @@
         <v>25</v>
       </c>
       <c r="C66">
+        <v>20</v>
+      </c>
+      <c r="D66">
         <v>19</v>
       </c>
-      <c r="D66">
-        <v>18</v>
-      </c>
       <c r="E66">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1705,13 +1705,13 @@
         <v>26</v>
       </c>
       <c r="C67">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D67">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E67">
-        <v>88</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1722,13 +1722,13 @@
         <v>26</v>
       </c>
       <c r="C68">
+        <v>26</v>
+      </c>
+      <c r="D68">
         <v>25</v>
       </c>
-      <c r="D68">
-        <v>24</v>
-      </c>
       <c r="E68">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1739,10 +1739,10 @@
         <v>26</v>
       </c>
       <c r="C69">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D69">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69">
         <v>100</v>
@@ -1756,10 +1756,10 @@
         <v>26</v>
       </c>
       <c r="C70">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D70">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E70">
         <v>100</v>
@@ -1773,13 +1773,13 @@
         <v>27</v>
       </c>
       <c r="C71">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E71">
-        <v>88</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1790,13 +1790,13 @@
         <v>27</v>
       </c>
       <c r="C72">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D72">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E72">
-        <v>84</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1807,13 +1807,13 @@
         <v>27</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D73">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E73">
-        <v>73.90000000000001</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1824,13 +1824,13 @@
         <v>27</v>
       </c>
       <c r="C74">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D74">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E74">
-        <v>73.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1841,13 +1841,13 @@
         <v>28</v>
       </c>
       <c r="C75">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="C76">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E76">
-        <v>15.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>28</v>
       </c>
       <c r="C77">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D77">
         <v>2</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>28</v>
       </c>
       <c r="C78">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D78">
         <v>4</v>
       </c>
       <c r="E78">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1909,7 +1909,7 @@
         <v>29</v>
       </c>
       <c r="C79">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>29</v>
       </c>
       <c r="C80">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
       <c r="E80">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>29</v>
       </c>
       <c r="C81">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>29</v>
       </c>
       <c r="C82">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D82">
         <v>2</v>
       </c>
       <c r="E82">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1977,10 +1977,10 @@
         <v>30</v>
       </c>
       <c r="C83">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D83">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E83">
         <v>100</v>
@@ -1994,10 +1994,10 @@
         <v>30</v>
       </c>
       <c r="C84">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D84">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E84">
         <v>100</v>
@@ -2011,10 +2011,10 @@
         <v>30</v>
       </c>
       <c r="C85">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D85">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E85">
         <v>100</v>
@@ -2028,10 +2028,10 @@
         <v>30</v>
       </c>
       <c r="C86">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D86">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E86">
         <v>100</v>
@@ -2045,10 +2045,10 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D87">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E87">
         <v>100</v>
@@ -2062,13 +2062,13 @@
         <v>31</v>
       </c>
       <c r="C88">
+        <v>26</v>
+      </c>
+      <c r="D88">
         <v>25</v>
       </c>
-      <c r="D88">
-        <v>24</v>
-      </c>
       <c r="E88">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2079,10 +2079,10 @@
         <v>31</v>
       </c>
       <c r="C89">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D89">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E89">
         <v>100</v>
@@ -2096,10 +2096,10 @@
         <v>31</v>
       </c>
       <c r="C90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E90">
         <v>100</v>
@@ -2113,13 +2113,13 @@
         <v>32</v>
       </c>
       <c r="C91">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D91">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E91">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2130,10 +2130,10 @@
         <v>32</v>
       </c>
       <c r="C92">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E92">
         <v>100</v>
@@ -2147,10 +2147,10 @@
         <v>32</v>
       </c>
       <c r="C93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E93">
         <v>100</v>
@@ -2164,13 +2164,13 @@
         <v>32</v>
       </c>
       <c r="C94">
+        <v>20</v>
+      </c>
+      <c r="D94">
         <v>19</v>
       </c>
-      <c r="D94">
-        <v>18</v>
-      </c>
       <c r="E94">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2181,10 +2181,10 @@
         <v>33</v>
       </c>
       <c r="C95">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D95">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E95">
         <v>100</v>
@@ -2198,10 +2198,10 @@
         <v>33</v>
       </c>
       <c r="C96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E96">
         <v>100</v>
@@ -2215,10 +2215,10 @@
         <v>33</v>
       </c>
       <c r="C97">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D97">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E97">
         <v>100</v>
@@ -2232,10 +2232,10 @@
         <v>33</v>
       </c>
       <c r="C98">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D98">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E98">
         <v>100</v>
@@ -2249,13 +2249,13 @@
         <v>34</v>
       </c>
       <c r="C99">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D99">
         <v>22</v>
       </c>
       <c r="E99">
-        <v>81.5</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2266,13 +2266,13 @@
         <v>34</v>
       </c>
       <c r="C100">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>22</v>
       </c>
       <c r="E100">
-        <v>84.59999999999999</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2283,13 +2283,13 @@
         <v>34</v>
       </c>
       <c r="C101">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D101">
         <v>10</v>
       </c>
       <c r="E101">
-        <v>43.5</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2300,13 +2300,13 @@
         <v>34</v>
       </c>
       <c r="C102">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D102">
         <v>18</v>
       </c>
       <c r="E102">
-        <v>90</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2317,13 +2317,13 @@
         <v>35</v>
       </c>
       <c r="C103">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D103">
         <v>2</v>
       </c>
       <c r="E103">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2334,13 +2334,13 @@
         <v>35</v>
       </c>
       <c r="C104">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D104">
         <v>2</v>
       </c>
       <c r="E104">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2351,13 +2351,13 @@
         <v>35</v>
       </c>
       <c r="C105">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D105">
         <v>4</v>
       </c>
       <c r="E105">
-        <v>16</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2368,13 +2368,13 @@
         <v>35</v>
       </c>
       <c r="C106">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D106">
         <v>4</v>
       </c>
       <c r="E106">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2385,13 +2385,13 @@
         <v>36</v>
       </c>
       <c r="C107">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D107">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E107">
-        <v>60</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2402,13 +2402,13 @@
         <v>36</v>
       </c>
       <c r="C108">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D108">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E108">
-        <v>72</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2419,13 +2419,13 @@
         <v>36</v>
       </c>
       <c r="C109">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D109">
         <v>12</v>
       </c>
       <c r="E109">
-        <v>48</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2436,13 +2436,13 @@
         <v>36</v>
       </c>
       <c r="C110">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110">
-        <v>25</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2453,7 +2453,7 @@
         <v>37</v>
       </c>
       <c r="C111">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -2470,7 +2470,7 @@
         <v>37</v>
       </c>
       <c r="C112">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -2487,7 +2487,7 @@
         <v>37</v>
       </c>
       <c r="C113">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>37</v>
       </c>
       <c r="C114">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -2521,13 +2521,13 @@
         <v>38</v>
       </c>
       <c r="C115">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D115">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E115">
-        <v>64.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2538,13 +2538,13 @@
         <v>38</v>
       </c>
       <c r="C116">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D116">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E116">
-        <v>43.2</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2555,13 +2555,13 @@
         <v>38</v>
       </c>
       <c r="C117">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D117">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E117">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2572,13 +2572,13 @@
         <v>38</v>
       </c>
       <c r="C118">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>10</v>
       </c>
       <c r="E118">
-        <v>31.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2589,10 +2589,10 @@
         <v>39</v>
       </c>
       <c r="C119">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D119">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E119">
         <v>100</v>
@@ -2606,10 +2606,10 @@
         <v>39</v>
       </c>
       <c r="C120">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D120">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E120">
         <v>100</v>
@@ -2623,10 +2623,10 @@
         <v>39</v>
       </c>
       <c r="C121">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D121">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E121">
         <v>100</v>
@@ -2640,10 +2640,10 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D122">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E122">
         <v>100</v>
@@ -2657,7 +2657,7 @@
         <v>40</v>
       </c>
       <c r="C123">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -2674,7 +2674,7 @@
         <v>40</v>
       </c>
       <c r="C124">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -2691,13 +2691,13 @@
         <v>40</v>
       </c>
       <c r="C125">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2708,7 +2708,7 @@
         <v>40</v>
       </c>
       <c r="C126">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -2725,7 +2725,7 @@
         <v>41</v>
       </c>
       <c r="C127">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>41</v>
       </c>
       <c r="C128">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2759,13 +2759,13 @@
         <v>41</v>
       </c>
       <c r="C129">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2776,7 +2776,7 @@
         <v>41</v>
       </c>
       <c r="C130">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -2793,13 +2793,13 @@
         <v>42</v>
       </c>
       <c r="C131">
+        <v>26</v>
+      </c>
+      <c r="D131">
         <v>25</v>
       </c>
-      <c r="D131">
-        <v>24</v>
-      </c>
       <c r="E131">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2810,13 +2810,13 @@
         <v>42</v>
       </c>
       <c r="C132">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D132">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E132">
-        <v>80</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2827,13 +2827,13 @@
         <v>42</v>
       </c>
       <c r="C133">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D133">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E133">
-        <v>87</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2844,13 +2844,13 @@
         <v>42</v>
       </c>
       <c r="C134">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D134">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E134">
-        <v>89.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2861,13 +2861,13 @@
         <v>43</v>
       </c>
       <c r="C135">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D135">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E135">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2878,10 +2878,10 @@
         <v>43</v>
       </c>
       <c r="C136">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D136">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E136">
         <v>100</v>
@@ -2895,13 +2895,13 @@
         <v>43</v>
       </c>
       <c r="C137">
+        <v>24</v>
+      </c>
+      <c r="D137">
         <v>23</v>
       </c>
-      <c r="D137">
-        <v>22</v>
-      </c>
       <c r="E137">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2912,13 +2912,13 @@
         <v>43</v>
       </c>
       <c r="C138">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D138">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E138">
-        <v>89.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2929,13 +2929,13 @@
         <v>44</v>
       </c>
       <c r="C139">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D139">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E139">
-        <v>88</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2946,13 +2946,13 @@
         <v>44</v>
       </c>
       <c r="C140">
+        <v>26</v>
+      </c>
+      <c r="D140">
         <v>25</v>
       </c>
-      <c r="D140">
-        <v>24</v>
-      </c>
       <c r="E140">
-        <v>96</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2963,10 +2963,10 @@
         <v>44</v>
       </c>
       <c r="C141">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D141">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E141">
         <v>100</v>
@@ -2980,10 +2980,10 @@
         <v>44</v>
       </c>
       <c r="C142">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D142">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E142">
         <v>100</v>
@@ -2997,7 +2997,7 @@
         <v>45</v>
       </c>
       <c r="C143">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -3014,13 +3014,13 @@
         <v>45</v>
       </c>
       <c r="C144">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D144">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E144">
-        <v>24.2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3031,13 +3031,13 @@
         <v>45</v>
       </c>
       <c r="C145">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D145">
         <v>5</v>
       </c>
       <c r="E145">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3048,13 +3048,13 @@
         <v>45</v>
       </c>
       <c r="C146">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E146">
-        <v>16.1</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3065,13 +3065,13 @@
         <v>46</v>
       </c>
       <c r="C147">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D147">
         <v>19</v>
       </c>
       <c r="E147">
-        <v>76</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3082,13 +3082,13 @@
         <v>46</v>
       </c>
       <c r="C148">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D148">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E148">
-        <v>68</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3099,13 +3099,13 @@
         <v>46</v>
       </c>
       <c r="C149">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D149">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E149">
-        <v>73.90000000000001</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3116,13 +3116,13 @@
         <v>46</v>
       </c>
       <c r="C150">
+        <v>20</v>
+      </c>
+      <c r="D150">
         <v>19</v>
       </c>
-      <c r="D150">
-        <v>18</v>
-      </c>
       <c r="E150">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3133,7 +3133,7 @@
         <v>47</v>
       </c>
       <c r="C151">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>47</v>
       </c>
       <c r="C152">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>47</v>
       </c>
       <c r="C153">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>47</v>
       </c>
       <c r="C154">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -3201,10 +3201,10 @@
         <v>48</v>
       </c>
       <c r="C155">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D155">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E155">
         <v>100</v>
@@ -3218,10 +3218,10 @@
         <v>48</v>
       </c>
       <c r="C156">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D156">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E156">
         <v>100</v>
@@ -3235,10 +3235,10 @@
         <v>48</v>
       </c>
       <c r="C157">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D157">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E157">
         <v>100</v>
@@ -3252,10 +3252,10 @@
         <v>48</v>
       </c>
       <c r="C158">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D158">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E158">
         <v>100</v>
@@ -3269,13 +3269,13 @@
         <v>49</v>
       </c>
       <c r="C159">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D159">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E159">
-        <v>92</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3286,10 +3286,10 @@
         <v>49</v>
       </c>
       <c r="C160">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D160">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E160">
         <v>100</v>
@@ -3303,13 +3303,13 @@
         <v>49</v>
       </c>
       <c r="C161">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D161">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E161">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3320,10 +3320,10 @@
         <v>49</v>
       </c>
       <c r="C162">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D162">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E162">
         <v>100</v>
@@ -3337,10 +3337,10 @@
         <v>50</v>
       </c>
       <c r="C163">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D163">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E163">
         <v>100</v>
@@ -3354,10 +3354,10 @@
         <v>50</v>
       </c>
       <c r="C164">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D164">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E164">
         <v>100</v>
@@ -3371,10 +3371,10 @@
         <v>51</v>
       </c>
       <c r="C165">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D165">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E165">
         <v>100</v>
@@ -3388,10 +3388,10 @@
         <v>51</v>
       </c>
       <c r="C166">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D166">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E166">
         <v>100</v>
@@ -3405,10 +3405,10 @@
         <v>51</v>
       </c>
       <c r="C167">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D167">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E167">
         <v>100</v>
@@ -3422,10 +3422,10 @@
         <v>51</v>
       </c>
       <c r="C168">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D168">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E168">
         <v>100</v>
@@ -3439,13 +3439,13 @@
         <v>52</v>
       </c>
       <c r="C169">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D169">
         <v>3</v>
       </c>
       <c r="E169">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3456,13 +3456,13 @@
         <v>52</v>
       </c>
       <c r="C170">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D170">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E170">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3473,13 +3473,13 @@
         <v>52</v>
       </c>
       <c r="C171">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D171">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E171">
-        <v>65.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3490,13 +3490,13 @@
         <v>52</v>
       </c>
       <c r="C172">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D172">
         <v>7</v>
       </c>
       <c r="E172">
-        <v>30.4</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3507,7 +3507,7 @@
         <v>53</v>
       </c>
       <c r="C173">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>53</v>
       </c>
       <c r="C174">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>53</v>
       </c>
       <c r="C175">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>53</v>
       </c>
       <c r="C176">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>54</v>
       </c>
       <c r="C177">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D177">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E177">
-        <v>29.7</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3592,13 +3592,13 @@
         <v>54</v>
       </c>
       <c r="C178">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D178">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E178">
-        <v>37.5</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3609,13 +3609,13 @@
         <v>54</v>
       </c>
       <c r="C179">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D179">
         <v>4</v>
       </c>
       <c r="E179">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3626,13 +3626,13 @@
         <v>54</v>
       </c>
       <c r="C180">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E180">
-        <v>20.9</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3694,13 +3694,13 @@
         <v>56</v>
       </c>
       <c r="C184">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E184">
-        <v>8.300000000000001</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3711,13 +3711,13 @@
         <v>56</v>
       </c>
       <c r="C185">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D185">
         <v>4</v>
       </c>
       <c r="E185">
-        <v>16.7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3745,13 +3745,13 @@
         <v>56</v>
       </c>
       <c r="C187">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D187">
         <v>1</v>
       </c>
       <c r="E187">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4000,10 +4000,10 @@
         <v>62</v>
       </c>
       <c r="C202">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D202">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E202">
         <v>100</v>
@@ -4017,10 +4017,10 @@
         <v>62</v>
       </c>
       <c r="C203">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D203">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E203">
         <v>100</v>
@@ -4034,13 +4034,13 @@
         <v>63</v>
       </c>
       <c r="C204">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D204">
         <v>16</v>
       </c>
       <c r="E204">
-        <v>69.59999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4051,13 +4051,13 @@
         <v>63</v>
       </c>
       <c r="C205">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D205">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E205">
-        <v>78.90000000000001</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206" spans="1:5">
